--- a/data/trans_orig/P42A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P42A-Clase-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>38404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>38404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26703</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26703</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>41372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>41372</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32383</t>
+          <t>32299</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32383</t>
+          <t>32299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41783</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41783</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29516</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29516</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>32837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>32837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>38926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>38926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>45073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70911</t>
+          <t>70640</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>45073</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70911</t>
+          <t>70640</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>34966</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59655</t>
+          <t>58871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>34966</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59655</t>
+          <t>58871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53596</t>
+          <t>53245</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53596</t>
+          <t>53245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67130</t>
+          <t>67615</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67130</t>
+          <t>67615</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49442</t>
+          <t>50081</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49442</t>
+          <t>50081</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52593</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52593</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22654</t>
+          <t>23305</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>43630</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22654</t>
+          <t>23305</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>43630</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>72820</t>
+          <t>71921</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72820</t>
+          <t>71921</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43456</t>
+          <t>43099</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>43456</t>
+          <t>43099</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>37857</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>37857</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>65887</t>
+          <t>66393</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>97391</t>
+          <t>96979</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>65887</t>
+          <t>66393</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>97391</t>
+          <t>96979</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>51546</t>
+          <t>53114</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>81042</t>
+          <t>81880</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>51546</t>
+          <t>53114</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>81042</t>
+          <t>81880</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>75332</t>
+          <t>73908</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>105850</t>
+          <t>105747</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>75332</t>
+          <t>73908</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>105850</t>
+          <t>105747</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -3267,12 +3267,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>87624</t>
+          <t>85988</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>87624</t>
+          <t>85988</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>72130</t>
+          <t>73905</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>72130</t>
+          <t>73905</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>216668</t>
+          <t>217163</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>272518</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>216668</t>
+          <t>217163</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>272518</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>179079</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>230349</t>
+          <t>229013</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>179079</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>230349</t>
+          <t>229013</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -3661,12 +3661,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>225706</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>282251</t>
+          <t>282422</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>225706</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>282251</t>
+          <t>282422</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>188269</t>
+          <t>186685</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>239937</t>
+          <t>239848</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>188269</t>
+          <t>186685</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>239937</t>
+          <t>239848</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3817,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>149703</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>199774</t>
+          <t>197687</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>149703</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>199774</t>
+          <t>197687</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -4228,12 +4228,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22321</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46088</t>
+          <t>47197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22321</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46088</t>
+          <t>47197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75830</t>
+          <t>74698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108814</t>
+          <t>109377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75830</t>
+          <t>74698</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>108814</t>
+          <t>109377</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77426</t>
+          <t>75521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110272</t>
+          <t>109813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77426</t>
+          <t>75521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110272</t>
+          <t>109813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -4462,12 +4462,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53832</t>
+          <t>55437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83315</t>
+          <t>85683</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53832</t>
+          <t>55437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83315</t>
+          <t>85683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45044</t>
+          <t>45024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45044</t>
+          <t>45024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -4700,12 +4700,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42938</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4715,12 +4715,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42938</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96362</t>
+          <t>96543</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>133488</t>
+          <t>133971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96362</t>
+          <t>96543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133488</t>
+          <t>133971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4856,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69386</t>
+          <t>68321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104163</t>
+          <t>103960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69386</t>
+          <t>68321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104163</t>
+          <t>103960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38068</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66261</t>
+          <t>67708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38068</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66261</t>
+          <t>67708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -5094,12 +5094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32982</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32982</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63510</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63510</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5250,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56155</t>
+          <t>55768</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>86540</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56155</t>
+          <t>55768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>86540</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -5328,12 +5328,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47194</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>73840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47194</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>73840</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5406,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26497</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49683</t>
+          <t>50375</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26497</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49683</t>
+          <t>50375</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -5566,12 +5566,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>52183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83671</t>
+          <t>84087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>52183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83671</t>
+          <t>84087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -5644,12 +5644,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94901</t>
+          <t>96147</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136523</t>
+          <t>137977</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94901</t>
+          <t>96147</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136523</t>
+          <t>137977</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>184217</t>
+          <t>182089</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>232550</t>
+          <t>231096</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5737,12 +5737,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>184217</t>
+          <t>182089</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>232550</t>
+          <t>231096</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133043</t>
+          <t>133904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178308</t>
+          <t>177139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>133043</t>
+          <t>133904</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178308</t>
+          <t>177139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -5878,12 +5878,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>119691</t>
+          <t>119220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>162733</t>
+          <t>160758</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119691</t>
+          <t>119220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>162733</t>
+          <t>160758</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -6038,12 +6038,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50194</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>81539</t>
+          <t>80973</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50194</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>81539</t>
+          <t>80973</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>155608</t>
+          <t>157410</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>201323</t>
+          <t>202524</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155608</t>
+          <t>157410</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>201323</t>
+          <t>202524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>185094</t>
+          <t>185483</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>233306</t>
+          <t>234651</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6229,12 +6229,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>185094</t>
+          <t>185483</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>233306</t>
+          <t>234651</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -6272,12 +6272,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>92606</t>
+          <t>93156</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>132440</t>
+          <t>133296</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>92606</t>
+          <t>93156</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>132440</t>
+          <t>133296</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6322,12 +6322,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>85783</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>123747</t>
+          <t>122078</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>85783</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>123747</t>
+          <t>122078</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>105995</t>
+          <t>103794</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>147998</t>
+          <t>146237</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>105995</t>
+          <t>103794</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>147998</t>
+          <t>146237</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>241233</t>
+          <t>241388</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>296750</t>
+          <t>296733</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>241233</t>
+          <t>241388</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>296750</t>
+          <t>296733</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>195345</t>
+          <t>194482</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>246887</t>
+          <t>246289</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>195345</t>
+          <t>194482</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>246887</t>
+          <t>246289</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>133839</t>
+          <t>130898</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>177549</t>
+          <t>174006</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>133839</t>
+          <t>130898</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>177549</t>
+          <t>174006</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -6822,12 +6822,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>85299</t>
+          <t>86269</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>124749</t>
+          <t>125534</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -6857,12 +6857,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>85299</t>
+          <t>86269</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>124749</t>
+          <t>125534</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>294555</t>
+          <t>293085</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>361354</t>
+          <t>360182</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>294555</t>
+          <t>293085</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>361354</t>
+          <t>360182</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -7060,12 +7060,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>625658</t>
+          <t>630759</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>720126</t>
+          <t>720468</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>625658</t>
+          <t>630759</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>720126</t>
+          <t>720468</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>857901</t>
+          <t>859500</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>966185</t>
+          <t>959697</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>857901</t>
+          <t>859500</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>966185</t>
+          <t>959697</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>610176</t>
+          <t>612740</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>703882</t>
+          <t>705704</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>610176</t>
+          <t>612740</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>703882</t>
+          <t>705704</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -7294,12 +7294,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>459136</t>
+          <t>459785</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>545382</t>
+          <t>545482</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>459136</t>
+          <t>459785</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>545382</t>
+          <t>545482</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7677,12 +7677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -7705,12 +7705,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33735</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60128</t>
+          <t>59255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33735</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60128</t>
+          <t>59255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -7783,12 +7783,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105780</t>
+          <t>107429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140397</t>
+          <t>141935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105780</t>
+          <t>107429</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140397</t>
+          <t>141935</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -7861,12 +7861,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74354</t>
+          <t>74374</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105888</t>
+          <t>106440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74354</t>
+          <t>74374</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105888</t>
+          <t>106440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -7939,12 +7939,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>38285</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65290</t>
+          <t>64051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>38285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65290</t>
+          <t>64051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64564</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64564</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -8255,12 +8255,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122300</t>
+          <t>122003</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158975</t>
+          <t>159431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122300</t>
+          <t>122003</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158975</t>
+          <t>159431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -8333,12 +8333,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72494</t>
+          <t>73254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105343</t>
+          <t>106152</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72494</t>
+          <t>73254</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105343</t>
+          <t>106152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -8411,12 +8411,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46648</t>
+          <t>47161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74551</t>
+          <t>75678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46648</t>
+          <t>47161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74551</t>
+          <t>75678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -8649,12 +8649,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51184</t>
+          <t>51234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8684,12 +8684,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51184</t>
+          <t>51234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -8727,12 +8727,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46704</t>
+          <t>47099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72449</t>
+          <t>73454</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46704</t>
+          <t>47099</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72449</t>
+          <t>73454</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>36350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>36350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -8883,12 +8883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -9043,12 +9043,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52729</t>
+          <t>54123</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9058,12 +9058,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52729</t>
+          <t>54123</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -9121,12 +9121,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>130340</t>
+          <t>132125</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>176117</t>
+          <t>175752</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130340</t>
+          <t>132125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>176117</t>
+          <t>175752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -9199,12 +9199,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>256664</t>
+          <t>258719</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>310530</t>
+          <t>313633</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>256664</t>
+          <t>258719</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>310530</t>
+          <t>313633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -9277,12 +9277,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136387</t>
+          <t>132504</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181008</t>
+          <t>180225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>136387</t>
+          <t>132504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>181008</t>
+          <t>180225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -9355,12 +9355,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91973</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132572</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>91973</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132572</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -9515,12 +9515,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51948</t>
+          <t>51977</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83448</t>
+          <t>83292</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51948</t>
+          <t>51977</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83448</t>
+          <t>83292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>165149</t>
+          <t>162805</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>211058</t>
+          <t>207986</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>165149</t>
+          <t>162805</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>211058</t>
+          <t>207986</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -9671,12 +9671,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>203191</t>
+          <t>205148</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>253284</t>
+          <t>252728</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>203191</t>
+          <t>205148</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>253284</t>
+          <t>252728</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73786</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>110232</t>
+          <t>112747</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>73786</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>110232</t>
+          <t>112747</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -9827,12 +9827,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>52649</t>
+          <t>53262</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>85674</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9842,12 +9842,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>52649</t>
+          <t>53262</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85674</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>81440</t>
+          <t>82657</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>121741</t>
+          <t>123889</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>81440</t>
+          <t>82657</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>121741</t>
+          <t>123889</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10037,12 +10037,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -10065,12 +10065,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>244022</t>
+          <t>244195</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>301161</t>
+          <t>301216</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10100,12 +10100,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>244022</t>
+          <t>244195</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>301161</t>
+          <t>301216</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -10143,12 +10143,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>236559</t>
+          <t>240191</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>295040</t>
+          <t>295206</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>236559</t>
+          <t>240191</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>295040</t>
+          <t>295206</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10221,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>92788</t>
+          <t>92303</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>132605</t>
+          <t>131490</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>92788</t>
+          <t>92303</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>132605</t>
+          <t>131490</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>68795</t>
+          <t>69785</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>105123</t>
+          <t>105164</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>68795</t>
+          <t>69785</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>105123</t>
+          <t>105164</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -10459,12 +10459,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>220597</t>
+          <t>218019</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>284655</t>
+          <t>284576</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>220597</t>
+          <t>218019</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>284655</t>
+          <t>284576</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -10537,12 +10537,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>697589</t>
+          <t>691184</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>795159</t>
+          <t>794182</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10552,12 +10552,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>697589</t>
+          <t>691184</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>795159</t>
+          <t>794182</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10587,12 +10587,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1040435</t>
+          <t>1047493</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1151029</t>
+          <t>1157180</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10630,12 +10630,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1040435</t>
+          <t>1047493</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1151029</t>
+          <t>1157180</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -10693,12 +10693,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>520112</t>
+          <t>518262</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>608869</t>
+          <t>601375</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10708,12 +10708,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>520112</t>
+          <t>518262</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>608869</t>
+          <t>601375</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10743,12 +10743,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -10771,12 +10771,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>358946</t>
+          <t>353803</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>433483</t>
+          <t>430067</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>358946</t>
+          <t>353803</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>433483</t>
+          <t>430067</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -11099,32 +11099,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11134,32 +11134,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -11177,32 +11177,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>57437</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>46554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>69448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11212,32 +11212,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>57437</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>46554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>69448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -11255,32 +11255,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85591</t>
+          <t>93297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73554</t>
+          <t>80011</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99945</t>
+          <t>107843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11290,32 +11290,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85591</t>
+          <t>93297</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73554</t>
+          <t>80011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99945</t>
+          <t>107843</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -11333,32 +11333,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86836</t>
+          <t>95343</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74672</t>
+          <t>81276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101132</t>
+          <t>110271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11368,32 +11368,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86836</t>
+          <t>95343</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74672</t>
+          <t>81276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101132</t>
+          <t>110271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -11411,32 +11411,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47352</t>
+          <t>52086</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37347</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58412</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11446,32 +11446,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>47352</t>
+          <t>52086</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37347</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58412</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -11489,17 +11489,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>276327</t>
+          <t>301842</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>276327</t>
+          <t>301842</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>276327</t>
+          <t>301842</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11524,17 +11524,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>276327</t>
+          <t>301842</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>276327</t>
+          <t>301842</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276327</t>
+          <t>301842</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>58252</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41227</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61715</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>58252</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41227</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61715</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -11727,32 +11727,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67256</t>
+          <t>77153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54187</t>
+          <t>65374</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79029</t>
+          <t>91046</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11762,32 +11762,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67256</t>
+          <t>77153</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54187</t>
+          <t>65374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79029</t>
+          <t>91046</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -11805,32 +11805,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68998</t>
+          <t>75286</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>61960</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80983</t>
+          <t>89267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11840,32 +11840,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68998</t>
+          <t>75286</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>61960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80983</t>
+          <t>89267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -11883,32 +11883,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37976</t>
+          <t>43328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62658</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37976</t>
+          <t>43328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62658</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -11961,17 +11961,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>279612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>279612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>279612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11996,17 +11996,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>279612</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>279612</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>279612</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -12121,32 +12121,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34887</t>
+          <t>36247</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50481</t>
+          <t>53508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12156,32 +12156,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34887</t>
+          <t>36247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50481</t>
+          <t>53508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -12199,32 +12199,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35764</t>
+          <t>39771</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12234,32 +12234,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35764</t>
+          <t>39771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -12277,32 +12277,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>22298</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12312,32 +12312,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>22298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -12355,32 +12355,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12390,32 +12390,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -12433,17 +12433,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>101540</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>101540</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101540</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12468,17 +12468,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101540</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>101540</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101540</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12515,32 +12515,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>47026</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53393</t>
+          <t>58820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12550,32 +12550,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>47026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53393</t>
+          <t>58820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -12593,32 +12593,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>133555</t>
+          <t>147478</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116548</t>
+          <t>130305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150394</t>
+          <t>164400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12628,32 +12628,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>133555</t>
+          <t>147478</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116548</t>
+          <t>130305</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150394</t>
+          <t>164400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -12671,32 +12671,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>152627</t>
+          <t>167281</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>136287</t>
+          <t>146689</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>171508</t>
+          <t>185816</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12706,32 +12706,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>152627</t>
+          <t>167281</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>136287</t>
+          <t>146689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171508</t>
+          <t>185816</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -12749,32 +12749,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>89028</t>
+          <t>102104</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75556</t>
+          <t>88571</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105189</t>
+          <t>119812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12784,32 +12784,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>89028</t>
+          <t>102104</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75556</t>
+          <t>88571</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105189</t>
+          <t>119812</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -12827,32 +12827,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>73299</t>
+          <t>83608</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88960</t>
+          <t>100371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12862,32 +12862,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>73299</t>
+          <t>83608</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88960</t>
+          <t>100371</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -12905,17 +12905,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12940,17 +12940,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12987,32 +12987,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>61267</t>
+          <t>71728</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80135</t>
+          <t>87174</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13022,32 +13022,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61267</t>
+          <t>71728</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80135</t>
+          <t>87174</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -13065,32 +13065,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>293162</t>
+          <t>207995</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>235346</t>
+          <t>190333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>392832</t>
+          <t>228888</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13100,32 +13100,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>293162</t>
+          <t>207995</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>235346</t>
+          <t>190333</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>392832</t>
+          <t>228888</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -13143,32 +13143,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>124879</t>
+          <t>138062</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82313</t>
+          <t>121465</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153006</t>
+          <t>155142</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13178,32 +13178,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>124879</t>
+          <t>138062</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82313</t>
+          <t>121465</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>153006</t>
+          <t>155142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -13221,32 +13221,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>73378</t>
+          <t>80603</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47939</t>
+          <t>68046</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>91733</t>
+          <t>96308</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13256,32 +13256,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>73378</t>
+          <t>80603</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>47939</t>
+          <t>68046</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>91733</t>
+          <t>96308</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -13299,32 +13299,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>49558</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>38476</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>58999</t>
+          <t>61163</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13334,32 +13334,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>49558</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>38476</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58999</t>
+          <t>61163</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -13377,17 +13377,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>597428</t>
+          <t>547946</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>597428</t>
+          <t>547946</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>597428</t>
+          <t>547946</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13412,17 +13412,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>597428</t>
+          <t>547946</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>597428</t>
+          <t>547946</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>597428</t>
+          <t>547946</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -13459,32 +13459,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>64402</t>
+          <t>72752</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>59804</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>86760</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13494,32 +13494,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>64402</t>
+          <t>72752</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>59804</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>86760</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -13537,32 +13537,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>190683</t>
+          <t>207270</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>173296</t>
+          <t>188747</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>208162</t>
+          <t>225256</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13572,32 +13572,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>190683</t>
+          <t>207270</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>173296</t>
+          <t>188747</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>208162</t>
+          <t>225256</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -13615,32 +13615,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>107930</t>
+          <t>118879</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>92898</t>
+          <t>102215</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>126004</t>
+          <t>135280</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13650,32 +13650,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>107930</t>
+          <t>118879</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>92898</t>
+          <t>102215</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>126004</t>
+          <t>135280</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -13693,32 +13693,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>58329</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>45820</t>
+          <t>52474</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>80293</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13728,32 +13728,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>58329</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>45820</t>
+          <t>52474</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>80293</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -13771,32 +13771,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>27045</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>37799</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13806,32 +13806,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>27045</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>37799</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -13849,17 +13849,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>448389</t>
+          <t>491530</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>448389</t>
+          <t>491530</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>448389</t>
+          <t>491530</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13884,17 +13884,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>448389</t>
+          <t>491530</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>448389</t>
+          <t>491530</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>448389</t>
+          <t>491530</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>188313</t>
+          <t>215755</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>163500</t>
+          <t>193181</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>211696</t>
+          <t>238623</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -13966,32 +13966,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>188313</t>
+          <t>215755</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>163500</t>
+          <t>193181</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>211696</t>
+          <t>238623</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -14009,32 +14009,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>764338</t>
+          <t>723244</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>696923</t>
+          <t>688458</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>915962</t>
+          <t>759873</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14044,32 +14044,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>764338</t>
+          <t>723244</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>696923</t>
+          <t>688458</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>915962</t>
+          <t>759873</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -14087,32 +14087,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>566450</t>
+          <t>626481</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>503938</t>
+          <t>591292</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>606914</t>
+          <t>666437</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14122,32 +14122,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>566450</t>
+          <t>626481</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>503938</t>
+          <t>591292</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>606914</t>
+          <t>666437</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -14165,32 +14165,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>389977</t>
+          <t>433659</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>342426</t>
+          <t>397915</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>423509</t>
+          <t>461756</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -14200,32 +14200,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>389977</t>
+          <t>433659</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>342426</t>
+          <t>397915</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>423509</t>
+          <t>461756</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -14243,32 +14243,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>253746</t>
+          <t>281057</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>222542</t>
+          <t>251599</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>283542</t>
+          <t>307259</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -14278,32 +14278,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>253746</t>
+          <t>281057</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>222542</t>
+          <t>251599</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>283542</t>
+          <t>307259</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -14321,17 +14321,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2162824</t>
+          <t>2280196</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2162824</t>
+          <t>2280196</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2162824</t>
+          <t>2280196</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -14356,17 +14356,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2162824</t>
+          <t>2280196</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2162824</t>
+          <t>2280196</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2162824</t>
+          <t>2280196</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
